--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,83 +656,86 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44104</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,8 +781,11 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +831,11 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +881,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,55 +903,59 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>1900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>800</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>2500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>300</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,23 +1001,26 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>900</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1017,8 +1036,8 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1032,8 +1051,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1047,7 +1069,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
         <v>0</v>
@@ -1073,14 +1095,17 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3" t="s">
-        <v>3</v>
+      <c r="P15" s="3">
+        <v>0</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,55 +1120,59 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E17" s="3">
         <v>7700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>13400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>33000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>10800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1151,46 +1180,49 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-13400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-33000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-2700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-5000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1240,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1217,46 +1250,49 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>14000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1264,69 +1300,72 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-12800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-13100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-32900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-11000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-9400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-5600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="E22" s="3">
         <v>1800</v>
       </c>
       <c r="F22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="G22" s="3">
         <v>2200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>800</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1343,61 +1382,67 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
+      <c r="P22" s="3">
+        <v>0</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-13200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-33000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-5600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5900</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1488,11 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,102 +1538,111 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-13200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-33000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-11000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-5600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-3800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5900</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-13200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-33000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-11000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-5600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-3800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5900</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1688,11 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1738,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1788,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1838,11 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1781,93 +1850,99 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-14000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-13200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-33000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-5600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-3800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5900</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,107 +1988,116 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-13200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-33000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-5600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-3800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5900</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44104</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2115,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,41 +2135,42 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>20300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>36200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>56800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>31100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>41100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>53700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>34700</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,8 +2183,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2144,8 +2233,11 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2191,8 +2283,11 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2238,41 +2333,44 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1000</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1500</v>
       </c>
       <c r="I45" s="3">
         <v>1500</v>
       </c>
       <c r="J45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,41 +2383,44 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E46" s="3">
         <v>13100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>38100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>57800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>75700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>32600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>44300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>54200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>34900</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,8 +2433,11 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2379,41 +2483,44 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>83300</v>
+      </c>
+      <c r="E48" s="3">
         <v>82400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>72500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>58700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>44800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>37200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>26400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24800</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,8 +2533,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2473,8 +2583,11 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2633,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,8 +2683,11 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2579,7 +2698,7 @@
         <v>300</v>
       </c>
       <c r="F52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>1100</v>
@@ -2599,8 +2718,8 @@
       <c r="L52" s="3">
         <v>1100</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>1100</v>
       </c>
       <c r="N52" s="3" t="s">
         <v>3</v>
@@ -2614,8 +2733,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,41 +2783,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>87100</v>
+      </c>
+      <c r="E54" s="3">
         <v>95700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>100900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>111600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>117600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>121700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>70900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>74900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>81700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>60700</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2833,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2855,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,40 +2875,41 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>7200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6100</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4300</v>
       </c>
       <c r="L57" s="3">
         <v>4300</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
+      <c r="M57" s="3">
+        <v>4300</v>
       </c>
       <c r="N57" s="3" t="s">
         <v>3</v>
@@ -2793,8 +2923,11 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2813,8 +2946,8 @@
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2828,8 +2961,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2840,41 +2973,44 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E59" s="3">
         <v>7200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2887,41 +3023,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E60" s="3">
         <v>9200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>12500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>6200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>4900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4500</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,41 +3073,44 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>42400</v>
+      </c>
+      <c r="E61" s="3">
         <v>41000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>37700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>36200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>33100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>31600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
         <v>0</v>
       </c>
@@ -2981,8 +3123,11 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2999,23 +3144,23 @@
         <v>800</v>
       </c>
       <c r="H62" s="3">
+        <v>800</v>
+      </c>
+      <c r="I62" s="3">
         <v>11600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>600</v>
       </c>
       <c r="K62" s="3">
         <v>600</v>
       </c>
       <c r="L62" s="3">
+        <v>600</v>
+      </c>
+      <c r="M62" s="3">
         <v>500</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3028,8 +3173,11 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3223,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3273,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,41 +3323,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E66" s="3">
         <v>51000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>47300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>48500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>46300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>8200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5100</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3373,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3395,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3443,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3493,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3543,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,41 +3593,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-158000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-147400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-138000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-127700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-117600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-102800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-107400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-94100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-61200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-50100</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3643,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3693,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3743,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,41 +3793,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E76" s="3">
         <v>44800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>53600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>63200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>71300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>68800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>62700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>67900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>75900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>55700</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +3843,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,107 +3893,116 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44104</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-13200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-33000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-5600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-3800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5900</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,8 +4020,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3844,11 +4042,11 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
         <v>0</v>
       </c>
@@ -3864,14 +4062,17 @@
       <c r="O83" s="3">
         <v>0</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
+      <c r="P83" s="3">
+        <v>0</v>
       </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4118,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4168,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4218,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4268,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4318,61 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-8400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-10600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="L89" s="3">
-        <v>-4800</v>
       </c>
       <c r="M89" s="3">
         <v>-4800</v>
       </c>
       <c r="N89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="O89" s="3">
         <v>-1500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-2300</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4390,59 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>100</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
       </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4488,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4538,61 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5200</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,8 +4610,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4425,8 +4658,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4708,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4758,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,8 +4808,11 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -4578,51 +4823,54 @@
         <v>0</v>
       </c>
       <c r="F100" s="3">
+        <v>0</v>
+      </c>
+      <c r="G100" s="3">
         <v>1300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>27300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>3600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>2800</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F101" s="3">
         <v>0</v>
@@ -4634,77 +4882,83 @@
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-8500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-15800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-20600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>43100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-10100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-12600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>19000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-4300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4600</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,86 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -784,8 +788,11 @@
       <c r="R8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -834,8 +841,11 @@
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -884,8 +894,11 @@
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -904,58 +917,62 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E12" s="3">
         <v>1400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>1900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>800</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>2500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>300</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1004,26 +1021,29 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>21000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>900</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1039,8 +1059,8 @@
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1054,8 +1074,11 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1072,7 +1095,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1098,14 +1121,17 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3" t="s">
-        <v>3</v>
+      <c r="Q15" s="3">
+        <v>0</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1121,58 +1147,62 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>25200</v>
+      </c>
+      <c r="E17" s="3">
         <v>8900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>7700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>13400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>33000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1180,49 +1210,52 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-8700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-13400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-33000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-10800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-2700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1241,8 +1274,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1250,49 +1284,52 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>14000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1300,75 +1337,78 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-8800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-8300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-7800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-12800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-13100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-32900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-11000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-9400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-5600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>800</v>
+      </c>
+      <c r="E22" s="3">
         <v>1700</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1800</v>
       </c>
       <c r="F22" s="3">
         <v>1800</v>
       </c>
       <c r="G22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="H22" s="3">
         <v>2200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>800</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1385,64 +1425,70 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
+      <c r="Q22" s="3">
+        <v>0</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-13200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-33000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-5600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-3800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1491,8 +1537,11 @@
       <c r="R24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1541,108 +1590,117 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-13200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-33000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-11000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-5600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-3800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-13200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-33000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-11000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-5600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-3800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1691,8 +1749,11 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1741,8 +1802,11 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1791,8 +1855,11 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1841,8 +1908,11 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1850,99 +1920,105 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-14000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-13200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-33000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-5600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-3800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1991,113 +2067,122 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-13200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-33000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-5600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-3800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2116,8 +2201,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2136,44 +2222,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E41" s="3">
         <v>2000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>20300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>36200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>56800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>74200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>41100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>34700</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2186,8 +2273,11 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2236,8 +2326,11 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2286,8 +2379,11 @@
       <c r="R43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2336,44 +2432,47 @@
       <c r="R44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E45" s="3">
         <v>1400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1500</v>
       </c>
       <c r="J45" s="3">
         <v>1500</v>
       </c>
       <c r="K45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="L45" s="3">
         <v>3200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2386,44 +2485,47 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E46" s="3">
         <v>3500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>38100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>57800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>75700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>32600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>44300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>54200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>34900</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2436,8 +2538,11 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2486,44 +2591,47 @@
       <c r="R47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E48" s="3">
         <v>83300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>82400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>72500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>58700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>44800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>37200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>26400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24800</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,8 +2644,11 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2586,8 +2697,11 @@
       <c r="R49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2636,8 +2750,11 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2686,8 +2803,11 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2701,7 +2821,7 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
         <v>1100</v>
@@ -2721,8 +2841,8 @@
       <c r="M52" s="3">
         <v>1100</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="N52" s="3">
+        <v>1100</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2736,8 +2856,11 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2786,44 +2909,47 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>97000</v>
+      </c>
+      <c r="E54" s="3">
         <v>87100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>95700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>100900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>111600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>117600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>121700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>70900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>74900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>81700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>60700</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,8 +2962,11 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2856,8 +2985,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2876,43 +3006,44 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E57" s="3">
         <v>2900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>4700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>7200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6100</v>
-      </c>
-      <c r="L57" s="3">
-        <v>4300</v>
       </c>
       <c r="M57" s="3">
         <v>4300</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>4300</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -2926,8 +3057,11 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2949,8 +3083,8 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2964,8 +3098,8 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
@@ -2976,44 +3110,47 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E59" s="3">
         <v>6000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3026,44 +3163,47 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E60" s="3">
         <v>9000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>11500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>12500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>6200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>4900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4500</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3076,44 +3216,47 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>63300</v>
+      </c>
+      <c r="E61" s="3">
         <v>42400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>41000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>37700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>36200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>33100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>31600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
         <v>0</v>
       </c>
@@ -3126,13 +3269,16 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E62" s="3">
         <v>800</v>
@@ -3147,23 +3293,23 @@
         <v>800</v>
       </c>
       <c r="I62" s="3">
+        <v>800</v>
+      </c>
+      <c r="J62" s="3">
         <v>11600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>700</v>
-      </c>
-      <c r="K62" s="3">
-        <v>600</v>
       </c>
       <c r="L62" s="3">
         <v>600</v>
       </c>
       <c r="M62" s="3">
+        <v>600</v>
+      </c>
+      <c r="N62" s="3">
         <v>500</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3176,8 +3322,11 @@
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3226,8 +3375,11 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3276,8 +3428,11 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3326,44 +3481,47 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E66" s="3">
         <v>52100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>51000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>48500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>46300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>52800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>8200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5100</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3376,8 +3534,11 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3396,8 +3557,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3446,8 +3608,11 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3496,8 +3661,11 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3546,8 +3714,11 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3596,44 +3767,47 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-183900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-158000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-147400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-138000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-127700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-117600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-102800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-107400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-94100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-61200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-50100</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3646,8 +3820,11 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3696,8 +3873,11 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3746,8 +3926,11 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3796,44 +3979,47 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E76" s="3">
         <v>35000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>44800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>53600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>63200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>71300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>68800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>62700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>67900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>75900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>55700</v>
       </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3846,8 +4032,11 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3896,113 +4085,122 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-13200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-33000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-5600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-3800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4021,8 +4219,9 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4045,11 +4244,11 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
         <v>0</v>
       </c>
@@ -4065,14 +4264,17 @@
       <c r="P83" s="3">
         <v>0</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4121,8 +4323,11 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4171,8 +4376,11 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4221,8 +4429,11 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4271,8 +4482,11 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4321,58 +4535,64 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-8400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-10600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="M89" s="3">
-        <v>-4800</v>
       </c>
       <c r="N89" s="3">
         <v>-4800</v>
       </c>
       <c r="O89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="P89" s="3">
         <v>-1500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4391,58 +4611,62 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>100</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4491,8 +4715,11 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4541,58 +4768,64 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-5100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4611,8 +4844,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4661,8 +4895,11 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4711,8 +4948,11 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4761,8 +5001,11 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4811,13 +5054,16 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>13200</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
@@ -4826,43 +5072,46 @@
         <v>0</v>
       </c>
       <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
         <v>1300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>27300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>3600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>2800</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4872,8 +5121,8 @@
       <c r="E101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -4885,80 +5134,86 @@
         <v>0</v>
       </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>100</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-9800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-8500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-15800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-20600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>43100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-10100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>19000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-4300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,90 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -791,8 +795,11 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +851,11 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +907,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,61 +931,65 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E12" s="3">
         <v>1200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>1900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>1000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>800</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>2500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,29 +1041,32 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>21000</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1062,8 +1082,8 @@
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1077,13 +1097,16 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="E15" s="3">
         <v>100</v>
@@ -1098,7 +1121,7 @@
         <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -1124,14 +1147,17 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>3</v>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,61 +1174,65 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E17" s="3">
         <v>25200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>13400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>33000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5000</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1210,52 +1240,55 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="F18" s="3">
         <v>-8900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-7700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-11200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-13400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-10800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-6100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-5000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,8 +1308,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1284,52 +1318,55 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>14000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>-200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1337,81 +1374,84 @@
         <v>3</v>
       </c>
       <c r="E21" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="F21" s="3">
         <v>-8800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-7500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-12800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-13100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-32900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-11000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-9400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-5600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5900</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E22" s="3">
         <v>800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1700</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1800</v>
       </c>
       <c r="G22" s="3">
         <v>1800</v>
       </c>
       <c r="H22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1428,67 +1468,73 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
+      <c r="R22" s="3">
+        <v>0</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-14900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-13200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-33000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-9500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-5600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5900</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1540,8 +1586,11 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,114 +1642,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-25900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-14900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-13200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-33000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-11000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-9500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-5600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5900</v>
       </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-25900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-14900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>4600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-13200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-33000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-11000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-9500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5900</v>
       </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1810,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1866,11 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1922,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,8 +1978,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1920,105 +1990,111 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-14000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-25900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-14900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>4600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-13200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-33000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-11000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-9500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-5600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5900</v>
       </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,119 +2146,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-25900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-14900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>4600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-13200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-33000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-11000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-9500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-5600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5900</v>
       </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2287,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,47 +2309,48 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E41" s="3">
         <v>8000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>20300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>36200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>56800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>41100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34700</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,8 +2363,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2329,8 +2419,11 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2382,8 +2475,11 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2435,47 +2531,50 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E45" s="3">
         <v>2000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>1500</v>
       </c>
       <c r="K45" s="3">
         <v>1500</v>
       </c>
       <c r="L45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2488,47 +2587,50 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E46" s="3">
         <v>10000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>38100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>57800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>75700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>32600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>44300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>54200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>34900</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2643,11 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2594,47 +2699,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>82400</v>
+      </c>
+      <c r="E48" s="3">
         <v>86700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>83300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>78500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>72500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>58700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>44800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>37200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>29500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>26400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24800</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,8 +2755,11 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2700,8 +2811,11 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2867,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,8 +2923,11 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2824,7 +2944,7 @@
         <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
         <v>1100</v>
@@ -2844,8 +2964,8 @@
       <c r="N52" s="3">
         <v>1100</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>1100</v>
       </c>
       <c r="P52" s="3" t="s">
         <v>3</v>
@@ -2859,8 +2979,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,47 +3035,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>89500</v>
+      </c>
+      <c r="E54" s="3">
         <v>97000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>87100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>95700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>100900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>111600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>117600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>121700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>70900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>74900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>81700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>60700</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3091,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3115,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,46 +3137,47 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>4300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>4700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>7200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>6100</v>
-      </c>
-      <c r="M57" s="3">
-        <v>4300</v>
       </c>
       <c r="N57" s="3">
         <v>4300</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
+      <c r="O57" s="3">
+        <v>4300</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>3</v>
@@ -3060,8 +3191,11 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3086,8 +3220,8 @@
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -3101,8 +3235,8 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -3113,47 +3247,50 @@
       <c r="S58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8800</v>
+      </c>
+      <c r="E59" s="3">
         <v>5300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3166,47 +3303,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E60" s="3">
         <v>7300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>11500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>6200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>4900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4500</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,47 +3359,50 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>64800</v>
+      </c>
+      <c r="E61" s="3">
         <v>63300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>42400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>41000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>37700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>36200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>33100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>31600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
         <v>0</v>
       </c>
@@ -3272,16 +3415,19 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E62" s="3">
         <v>1000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>800</v>
       </c>
       <c r="F62" s="3">
         <v>800</v>
@@ -3296,23 +3442,23 @@
         <v>800</v>
       </c>
       <c r="J62" s="3">
+        <v>800</v>
+      </c>
+      <c r="K62" s="3">
         <v>11600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>700</v>
-      </c>
-      <c r="L62" s="3">
-        <v>600</v>
       </c>
       <c r="M62" s="3">
         <v>600</v>
       </c>
       <c r="N62" s="3">
+        <v>600</v>
+      </c>
+      <c r="O62" s="3">
         <v>500</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3325,8 +3471,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3527,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3583,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,47 +3639,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E66" s="3">
         <v>71500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>48500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>52800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5100</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3695,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3719,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3773,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3829,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +3885,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,47 +3941,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-200000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-183900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-158000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-147400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-138000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-127700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-117600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-102800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-107400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-94100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-61200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-50100</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +3997,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4053,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4109,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,47 +4165,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E76" s="3">
         <v>25500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>35000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>44800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>53600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>63200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>71300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>68800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>62700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>67900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>75900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>55700</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4221,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,119 +4277,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-25900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-14900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>4600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-13200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-33000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-11000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-9500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-5600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5900</v>
       </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,13 +4418,14 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>100</v>
+        <v>5100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -4247,11 +4446,11 @@
         <v>100</v>
       </c>
       <c r="K83" s="3">
+        <v>100</v>
+      </c>
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -4267,14 +4466,17 @@
       <c r="Q83" s="3">
         <v>0</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4528,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4584,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4640,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4696,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,61 +4752,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-7200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-8400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-10600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="N89" s="3">
-        <v>-4800</v>
       </c>
       <c r="O89" s="3">
         <v>-4800</v>
       </c>
       <c r="P89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-1500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-2300</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,61 +4832,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>100</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
+      <c r="R91" s="3">
+        <v>0</v>
       </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +4942,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,61 +4998,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5200</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5078,9 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4898,8 +5132,11 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5188,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5244,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,17 +5300,20 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E100" s="3">
         <v>13200</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
@@ -5075,54 +5321,57 @@
         <v>0</v>
       </c>
       <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
         <v>1300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>56100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>27300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>3600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2800</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
       </c>
       <c r="G101" s="3">
         <v>0</v>
@@ -5137,83 +5386,89 @@
         <v>0</v>
       </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E102" s="3">
         <v>5900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-9800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-8500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-15800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-20600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>43100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-10100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>19000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-4300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,117 +656,121 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -798,31 +802,34 @@
       <c r="T8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+      <c r="D9" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -854,31 +861,34 @@
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+      <c r="D10" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="G10" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="H10" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I10" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="J10" s="3">
+        <v>-1300</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -910,8 +920,11 @@
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,64 +945,68 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>100</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>3400</v>
+      </c>
+      <c r="L12" s="3">
+        <v>3600</v>
+      </c>
+      <c r="M12" s="3">
+        <v>3200</v>
+      </c>
+      <c r="N12" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P12" s="3">
+        <v>800</v>
+      </c>
+      <c r="Q12" s="3">
         <v>2500</v>
       </c>
-      <c r="E12" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F12" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G12" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I12" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J12" s="3">
-        <v>3400</v>
-      </c>
-      <c r="K12" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L12" s="3">
-        <v>3200</v>
-      </c>
-      <c r="M12" s="3">
-        <v>1900</v>
-      </c>
-      <c r="N12" s="3">
-        <v>1000</v>
-      </c>
-      <c r="O12" s="3">
-        <v>800</v>
-      </c>
-      <c r="P12" s="3">
-        <v>2500</v>
-      </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>300</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,32 +1061,35 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>21000</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1085,8 +1105,8 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1100,8 +1120,11 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1109,7 +1132,7 @@
         <v>5000</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1124,7 +1147,7 @@
         <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1150,14 +1173,17 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>3</v>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,120 +1201,127 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E17" s="3">
         <v>15100</v>
       </c>
-      <c r="E17" s="3">
-        <v>25200</v>
-      </c>
       <c r="F17" s="3">
+        <v>4200</v>
+      </c>
+      <c r="G17" s="3">
         <v>8900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8700</v>
       </c>
-      <c r="I17" s="3">
-        <v>8300</v>
-      </c>
       <c r="J17" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K17" s="3">
         <v>11200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>13400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>33000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>6100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5000</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-12900</v>
       </c>
       <c r="E18" s="3">
-        <v>-25200</v>
+        <v>-15100</v>
       </c>
       <c r="F18" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-8900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-7700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8700</v>
       </c>
-      <c r="I18" s="3">
-        <v>-8300</v>
-      </c>
       <c r="J18" s="3">
+        <v>-7400</v>
+      </c>
+      <c r="K18" s="3">
         <v>-11200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-13400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-10800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-2700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-5000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,152 +1342,159 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-2200</v>
       </c>
       <c r="E20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="L20" s="3">
+        <v>14000</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>200</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Q20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>-1700</v>
-      </c>
-      <c r="K20" s="3">
-        <v>14000</v>
-      </c>
-      <c r="L20" s="3">
-        <v>100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>1200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>400</v>
-      </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-900</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-5800</v>
       </c>
       <c r="E21" s="3">
-        <v>-25000</v>
+        <v>-9300</v>
       </c>
       <c r="F21" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="G21" s="3">
         <v>-8800</v>
       </c>
-      <c r="G21" s="3">
-        <v>-7500</v>
-      </c>
       <c r="H21" s="3">
-        <v>-8300</v>
+        <v>-7700</v>
       </c>
       <c r="I21" s="3">
-        <v>-7800</v>
+        <v>-8600</v>
       </c>
       <c r="J21" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="K21" s="3">
         <v>-12800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-32900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-11000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-9400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5900</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1700</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1800</v>
       </c>
       <c r="H22" s="3">
         <v>1800</v>
       </c>
       <c r="I22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1471,93 +1511,99 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
+      <c r="S22" s="3">
+        <v>0</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-16100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-25900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-10600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-9400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-14900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-13200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-33000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5900</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1589,8 +1635,11 @@
       <c r="T24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,120 +1694,129 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-16100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-25900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-10600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-9400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-14900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-33000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-11000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-9500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-3800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-16100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-25900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-10600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-9400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-33000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-11000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-9500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-3800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1871,11 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1869,8 +1930,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +1989,11 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,120 +2048,129 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>2200</v>
       </c>
       <c r="E32" s="3">
+        <v>700</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>1700</v>
+      </c>
+      <c r="L32" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>200</v>
+      </c>
+      <c r="P32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>1700</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-14000</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>900</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-16100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-25900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-10600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-9400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-14900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-13200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-33000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-11000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-9500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-3800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,125 +2225,134 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-16100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-25900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-10600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-9400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-14900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-13200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-33000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-11000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-9500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-3800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2373,9 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,50 +2396,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E41" s="3">
         <v>4900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>20300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>36200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>56800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>31100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>41100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34700</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2366,8 +2453,11 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2422,31 +2512,34 @@
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2478,31 +2571,34 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2534,50 +2630,53 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="E45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H45" s="3">
-        <v>1800</v>
-      </c>
-      <c r="I45" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>1000</v>
-      </c>
-      <c r="K45" s="3">
-        <v>1500</v>
       </c>
       <c r="L45" s="3">
         <v>1500</v>
       </c>
       <c r="M45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>200</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,50 +2689,53 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E46" s="3">
         <v>6800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>10000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>38100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>57800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>75700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>32600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>44300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>54200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>34900</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2646,31 +2748,34 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2702,50 +2807,53 @@
       <c r="T47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>77300</v>
+      </c>
+      <c r="E48" s="3">
         <v>82400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>86700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>83300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>82400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>78500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>72500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>58700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>44800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>37200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>29500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>26400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>24800</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2758,8 +2866,11 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2814,8 +2925,11 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +2984,11 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,8 +3043,11 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2947,7 +3067,7 @@
         <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
         <v>1100</v>
@@ -2967,8 +3087,8 @@
       <c r="O52" s="3">
         <v>1100</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="P52" s="3">
+        <v>1100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -2982,8 +3102,11 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,50 +3161,53 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>85800</v>
+      </c>
+      <c r="E54" s="3">
         <v>89500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>97000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>87100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>95700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>100900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>111600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>117600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>70900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>74900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>81700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>60700</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,8 +3220,11 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3245,9 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,49 +3268,50 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1500</v>
       </c>
-      <c r="I57" s="3">
-        <v>4300</v>
-      </c>
       <c r="J57" s="3">
+        <v>500</v>
+      </c>
+      <c r="K57" s="3">
         <v>2900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>6100</v>
-      </c>
-      <c r="N57" s="3">
-        <v>4300</v>
       </c>
       <c r="O57" s="3">
         <v>4300</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3">
+        <v>4300</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3194,37 +3325,40 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
+      <c r="L58" s="3">
+        <v>0</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
@@ -3238,8 +3372,8 @@
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R58" s="3">
         <v>0</v>
@@ -3250,50 +3384,53 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>8800</v>
+        <v>2900</v>
       </c>
       <c r="E59" s="3">
-        <v>5300</v>
+        <v>3300</v>
       </c>
       <c r="F59" s="3">
-        <v>6000</v>
+        <v>3100</v>
       </c>
       <c r="G59" s="3">
-        <v>7200</v>
+        <v>2800</v>
       </c>
       <c r="H59" s="3">
-        <v>7300</v>
+        <v>4500</v>
       </c>
       <c r="I59" s="3">
-        <v>7100</v>
+        <v>3400</v>
       </c>
       <c r="J59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="K59" s="3">
         <v>9600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3306,50 +3443,53 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E60" s="3">
         <v>9700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>11500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>6200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>4900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4500</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3362,50 +3502,53 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>64800</v>
+        <v>72600</v>
       </c>
       <c r="E61" s="3">
-        <v>63300</v>
+        <v>65000</v>
       </c>
       <c r="F61" s="3">
+        <v>63500</v>
+      </c>
+      <c r="G61" s="3">
         <v>42400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>41000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>37700</v>
       </c>
-      <c r="I61" s="3">
-        <v>36200</v>
-      </c>
       <c r="J61" s="3">
+        <v>36300</v>
+      </c>
+      <c r="K61" s="3">
         <v>33100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>31600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3418,16 +3561,19 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>4100</v>
       </c>
       <c r="F62" s="3">
         <v>800</v>
@@ -3436,32 +3582,32 @@
         <v>800</v>
       </c>
       <c r="H62" s="3">
+        <v>700</v>
+      </c>
+      <c r="I62" s="3">
+        <v>700</v>
+      </c>
+      <c r="J62" s="3">
+        <v>700</v>
+      </c>
+      <c r="K62" s="3">
         <v>800</v>
       </c>
-      <c r="I62" s="3">
-        <v>800</v>
-      </c>
-      <c r="J62" s="3">
-        <v>800</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>600</v>
       </c>
       <c r="N62" s="3">
         <v>600</v>
       </c>
       <c r="O62" s="3">
+        <v>600</v>
+      </c>
+      <c r="P62" s="3">
         <v>500</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3474,8 +3620,11 @@
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3679,11 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3738,11 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,50 +3797,53 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E66" s="3">
         <v>78800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>71500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>48500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>46300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>8200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5100</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3698,8 +3856,11 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +3881,9 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +3938,11 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +3997,11 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4056,11 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,50 +4115,53 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-212900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-200000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-183900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-158000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-147400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-138000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-127700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-117600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-102800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-107400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-94100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-61200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-50100</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,8 +4174,11 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4233,11 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4292,11 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,50 +4351,53 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E76" s="3">
         <v>10700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>25500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>35000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>53600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>63200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>71300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>68800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>62700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>75900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>55700</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4224,8 +4410,11 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,125 +4469,134 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-16100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-25900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-10600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-9400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-14900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-13200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-33000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-11000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-9500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-3800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,13 +4617,14 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>5100</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
         <v>100</v>
@@ -4440,20 +4639,20 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K83" s="3">
         <v>100</v>
       </c>
       <c r="L83" s="3">
+        <v>100</v>
+      </c>
+      <c r="M83" s="3">
         <v>200</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
       <c r="N83" s="3">
         <v>0</v>
       </c>
@@ -4469,14 +4668,17 @@
       <c r="R83" s="3">
         <v>0</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
+      <c r="S83" s="3">
+        <v>0</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4733,11 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4792,11 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +4851,11 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +4910,11 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +4969,70 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-6900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-8400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-10600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="O89" s="3">
-        <v>-4800</v>
       </c>
       <c r="P89" s="3">
         <v>-4800</v>
       </c>
       <c r="Q89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="R89" s="3">
         <v>-1500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-2300</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,64 +5053,68 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-13900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>100</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
+      <c r="S91" s="3">
+        <v>0</v>
       </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5169,11 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5228,70 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5200</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,31 +5312,32 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -5135,8 +5369,11 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5428,11 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5487,11 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,20 +5546,23 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E100" s="3">
         <v>5500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>13200</v>
       </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
       <c r="G100" s="3">
         <v>0</v>
       </c>
@@ -5324,151 +5570,160 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>1300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>27300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>3600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2800</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="J101" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>100</v>
       </c>
-      <c r="S101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-9800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-8500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>43100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>19000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4600</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,98 +656,101 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -772,8 +775,8 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L8" s="3">
         <v>0</v>
@@ -805,35 +808,38 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E9" s="3">
         <v>3100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
@@ -864,35 +870,38 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-3100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1300</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -923,8 +932,11 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -946,67 +958,71 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3">
         <v>0</v>
       </c>
       <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
       <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
         <v>3400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>1900</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>800</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>2500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>300</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1064,35 +1080,38 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>21000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>900</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1108,8 +1127,8 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1123,8 +1142,11 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1135,7 +1157,7 @@
         <v>5000</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
@@ -1150,7 +1172,7 @@
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1176,14 +1198,17 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>3</v>
+      <c r="T15" s="3">
+        <v>0</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1202,126 +1227,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>13400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>33000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>6100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E18" s="3">
         <v>-12900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-15100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-4200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-8900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-7700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-8700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-7400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-11200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-13400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-33000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-10800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-6100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-2700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-5000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1343,20 +1375,21 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-2200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1370,134 +1403,140 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>-1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>14000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-6900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-9300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-8800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-7700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-8600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-7300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-32900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-11000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-9400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-5600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-3800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E22" s="3">
         <v>2200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1700</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1800</v>
       </c>
       <c r="I22" s="3">
         <v>1800</v>
       </c>
       <c r="J22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K22" s="3">
         <v>2200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>800</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1514,73 +1553,79 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
+      <c r="T22" s="3">
+        <v>0</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-12900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-10600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-9400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-10300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-14900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-13200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-33000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-5600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-3800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-5900</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1605,8 +1650,8 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1638,8 +1683,11 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1697,126 +1745,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-12900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-25900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-10600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-9400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-14900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-33000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-11000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-5600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-3800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-12900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-16100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-25900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-10600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-9400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-10300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-14900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-33000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-11000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-5600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-3800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-5900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1874,8 +1931,11 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,8 +1993,11 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1992,8 +2055,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2051,20 +2117,23 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>2200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2078,99 +2147,105 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-14000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-12900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-16100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-25900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-10600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-9400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-10300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-14900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-13200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-33000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-11000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-5600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-3800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-5900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2228,131 +2303,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-12900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-16100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-25900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-10600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-9400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-10300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-14900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-13200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-33000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-11000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-5600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-3800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-5900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2374,8 +2458,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2397,53 +2482,54 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>800</v>
+      </c>
+      <c r="E41" s="3">
         <v>6900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>20300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>36200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>56800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>74200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>31100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>41100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34700</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2456,8 +2542,11 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2515,8 +2604,11 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2541,8 +2633,8 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
@@ -2574,8 +2666,11 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2600,8 +2695,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2633,8 +2728,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2659,27 +2757,27 @@
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>1000</v>
-      </c>
-      <c r="L45" s="3">
-        <v>1500</v>
       </c>
       <c r="M45" s="3">
         <v>1500</v>
       </c>
       <c r="N45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2692,53 +2790,56 @@
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E46" s="3">
         <v>8100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>38100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>57800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>75700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>32600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>44300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>54200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>34900</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2751,8 +2852,11 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2777,8 +2881,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -2810,53 +2914,56 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>73100</v>
+      </c>
+      <c r="E48" s="3">
         <v>77300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>82400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>86700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>83300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>82400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>78500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>72500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>58700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>44800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>37200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>26400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24800</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2869,8 +2976,11 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2928,8 +3038,11 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2987,8 +3100,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3046,8 +3162,11 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3070,7 +3189,7 @@
         <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>1100</v>
@@ -3090,8 +3209,8 @@
       <c r="P52" s="3">
         <v>1100</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
+      <c r="Q52" s="3">
+        <v>1100</v>
       </c>
       <c r="R52" s="3" t="s">
         <v>3</v>
@@ -3105,8 +3224,11 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3164,53 +3286,56 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E54" s="3">
         <v>85800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>89500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>97000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>87100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>95700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>100900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>111600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>117600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>70900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>74900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>81700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>60700</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3223,8 +3348,11 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3246,8 +3374,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3269,8 +3398,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3278,43 +3408,43 @@
         <v>1500</v>
       </c>
       <c r="E57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>6100</v>
-      </c>
-      <c r="O57" s="3">
-        <v>4300</v>
       </c>
       <c r="P57" s="3">
         <v>4300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
+      <c r="Q57" s="3">
+        <v>4300</v>
       </c>
       <c r="R57" s="3" t="s">
         <v>3</v>
@@ -3328,13 +3458,16 @@
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
         <v>200</v>
@@ -3343,10 +3476,10 @@
         <v>200</v>
       </c>
       <c r="G58" s="3">
+        <v>200</v>
+      </c>
+      <c r="H58" s="3">
         <v>100</v>
-      </c>
-      <c r="H58" s="3">
-        <v>200</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
@@ -3355,13 +3488,13 @@
         <v>200</v>
       </c>
       <c r="K58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -3375,8 +3508,8 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3387,53 +3520,56 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E59" s="3">
         <v>2900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>4800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3446,53 +3582,56 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E60" s="3">
         <v>7500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>7300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>6200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>4900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4500</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3505,53 +3644,56 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E61" s="3">
         <v>72600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>65000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>63500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>42400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>41000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>37700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>36300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>33100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>31600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3564,25 +3706,28 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>900</v>
+      </c>
+      <c r="E62" s="3">
         <v>3600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4100</v>
-      </c>
-      <c r="F62" s="3">
-        <v>800</v>
       </c>
       <c r="G62" s="3">
         <v>800</v>
       </c>
       <c r="H62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="I62" s="3">
         <v>700</v>
@@ -3591,26 +3736,26 @@
         <v>700</v>
       </c>
       <c r="K62" s="3">
+        <v>700</v>
+      </c>
+      <c r="L62" s="3">
         <v>800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>600</v>
       </c>
       <c r="O62" s="3">
         <v>600</v>
       </c>
       <c r="P62" s="3">
+        <v>600</v>
+      </c>
+      <c r="Q62" s="3">
         <v>500</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,8 +3768,11 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3682,8 +3830,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3741,8 +3892,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3800,53 +3954,56 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E66" s="3">
         <v>83700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>78800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>71500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>51000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>47300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>48500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>46300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>8200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3859,8 +4016,11 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3882,8 +4042,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3941,8 +4102,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4000,8 +4164,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4059,8 +4226,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4118,53 +4288,56 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-227100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-212900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-200000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-183900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-158000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-147400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-138000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-127700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-117600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-102800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-107400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-94100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-61200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4177,8 +4350,11 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4236,8 +4412,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4295,8 +4474,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4354,53 +4536,56 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-8400</v>
+      </c>
+      <c r="E76" s="3">
         <v>2100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>25500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>35000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>53600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>63200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>71300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>68800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>62700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>67900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>75900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>55700</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4413,8 +4598,11 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4472,131 +4660,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-12900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-16100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-25900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-10600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-9400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-10300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-14900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-13200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-33000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-11000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-9500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-5600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-3800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-5900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4618,8 +4815,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4639,23 +4837,23 @@
         <v>100</v>
       </c>
       <c r="I83" s="3">
+        <v>100</v>
+      </c>
+      <c r="J83" s="3">
         <v>200</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
       <c r="K83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L83" s="3">
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
         <v>0</v>
       </c>
@@ -4671,14 +4869,17 @@
       <c r="S83" s="3">
         <v>0</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
+      <c r="T83" s="3">
+        <v>0</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4736,8 +4937,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4795,8 +4999,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4854,8 +5061,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4913,8 +5123,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4972,67 +5185,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-6400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-7200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-4900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-7900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-10600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-4800</v>
       </c>
       <c r="Q89" s="3">
         <v>-4800</v>
       </c>
       <c r="R89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="S89" s="3">
         <v>-1500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-2300</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5054,67 +5273,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-13900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>100</v>
       </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
+      <c r="T91" s="3">
+        <v>0</v>
       </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5172,8 +5395,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5231,8 +5457,11 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5240,58 +5469,61 @@
         <v>-400</v>
       </c>
       <c r="E94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-1300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5313,8 +5545,9 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5339,8 +5572,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -5372,8 +5605,11 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5431,8 +5667,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5490,8 +5729,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5549,23 +5791,26 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E100" s="3">
         <v>8700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>5500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>13200</v>
       </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
       <c r="H100" s="3">
         <v>0</v>
       </c>
@@ -5573,43 +5818,46 @@
         <v>0</v>
       </c>
       <c r="J100" s="3">
+        <v>0</v>
+      </c>
+      <c r="K100" s="3">
         <v>1300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>2100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>27300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2800</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5628,102 +5876,108 @@
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I101" s="3">
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>100</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-9800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-8500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-20600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>43100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-6100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,101 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -778,8 +782,8 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -811,38 +815,41 @@
       <c r="V8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E9" s="3">
         <v>2800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,38 +880,41 @@
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-1900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-3100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-2500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-1400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-1600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
@@ -935,8 +945,11 @@
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -959,8 +972,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -970,59 +984,62 @@
       <c r="E12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
+      <c r="F12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I12" s="3">
         <v>0</v>
       </c>
       <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
       <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
         <v>3400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3200</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>1900</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>1000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>800</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>2500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>300</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1083,38 +1100,41 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>-17300</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>21000</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1130,8 +1150,8 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3">
         <v>0</v>
@@ -1145,8 +1165,11 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1160,7 +1183,7 @@
         <v>5000</v>
       </c>
       <c r="G15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="H15" s="3">
         <v>100</v>
@@ -1175,7 +1198,7 @@
         <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1201,14 +1224,17 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>3</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1228,132 +1254,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E17" s="3">
         <v>11000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>12900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>15100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>8700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>13400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>33000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>10600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>6100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5000</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-11000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-12900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-15100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-4200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-8900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-7700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-8700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-7400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-11200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-13400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-33000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-10800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-10600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-6100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-2700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-5000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1376,23 +1409,24 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
       <c r="H20" s="3">
         <v>0</v>
       </c>
@@ -1406,140 +1440,146 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>14000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-6900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-9300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-8800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-7700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-8600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>5500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-32900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-9400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-5600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-3800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5900</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E22" s="3">
         <v>2400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1700</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1800</v>
       </c>
       <c r="J22" s="3">
         <v>1800</v>
       </c>
       <c r="K22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L22" s="3">
         <v>2200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>800</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P22" s="3">
         <v>0</v>
@@ -1556,76 +1596,82 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
+      <c r="U22" s="3">
+        <v>0</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-14300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-12900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-16100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-10600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-9400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-10300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-14900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-13200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-33000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-5600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-5900</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1653,8 +1699,8 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1686,8 +1732,11 @@
       <c r="V24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1748,132 +1797,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-14300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-12900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-16100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-25900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-10600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-9400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-33000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-9500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-5600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-3800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-14300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-12900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-16100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-25900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-10600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-9400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-10300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-33000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-9500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-5600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-3800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-5900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1934,8 +1992,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1996,8 +2057,11 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2058,8 +2122,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2120,23 +2187,26 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
       <c r="H32" s="3">
         <v>0</v>
       </c>
@@ -2150,102 +2220,108 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>1700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-14000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-14300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-12900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-25900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-10600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-9400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-10300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-13200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-33000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-9500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-5600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-3800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-5900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2306,137 +2382,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-14300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-12900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-25900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-10600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-9400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-10300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-13200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-33000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-9500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-5600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-3800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-5900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2459,8 +2544,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2483,56 +2569,57 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E41" s="3">
         <v>800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>20300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>36200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>56800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>31100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>41100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>34700</v>
       </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,8 +2632,11 @@
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2607,8 +2697,11 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2636,8 +2729,8 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2669,8 +2762,11 @@
       <c r="V43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2698,8 +2794,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2731,8 +2827,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2760,27 +2859,27 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3">
         <v>1000</v>
-      </c>
-      <c r="M45" s="3">
-        <v>1500</v>
       </c>
       <c r="N45" s="3">
         <v>1500</v>
       </c>
       <c r="O45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="P45" s="3">
         <v>3200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2793,56 +2892,59 @@
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>22100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>38100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>57800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>75700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>32600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>44300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>54200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>34900</v>
       </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,8 +2957,11 @@
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2884,8 +2989,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2917,56 +3022,59 @@
       <c r="V47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E48" s="3">
         <v>73100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>77300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>82400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>86700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>83300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>78500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>72500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>58700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>44800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>37200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>26400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24800</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2979,8 +3087,11 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3041,8 +3152,11 @@
       <c r="V49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3103,8 +3217,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3165,8 +3282,11 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3192,7 +3312,7 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>1100</v>
@@ -3212,8 +3332,8 @@
       <c r="Q52" s="3">
         <v>1100</v>
       </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
+      <c r="R52" s="3">
+        <v>1100</v>
       </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
@@ -3227,8 +3347,11 @@
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3289,56 +3412,59 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73400</v>
+      </c>
+      <c r="E54" s="3">
         <v>74800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>85800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>89500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>97000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>87100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>95700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>100900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>111600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>117600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>121700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>70900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>74900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>81700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>60700</v>
       </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3351,8 +3477,11 @@
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3375,8 +3504,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3399,55 +3529,56 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>1500</v>
+        <v>6100</v>
       </c>
       <c r="E57" s="3">
         <v>1500</v>
       </c>
       <c r="F57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>4700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>6100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>4300</v>
       </c>
       <c r="Q57" s="3">
         <v>4300</v>
       </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
+      <c r="R57" s="3">
+        <v>4300</v>
       </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
@@ -3461,8 +3592,11 @@
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3470,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -3479,10 +3613,10 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>200</v>
+      </c>
+      <c r="I58" s="3">
         <v>100</v>
-      </c>
-      <c r="I58" s="3">
-        <v>200</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -3491,13 +3625,13 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
@@ -3511,8 +3645,8 @@
       <c r="R58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3523,56 +3657,59 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>3400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>2900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3585,56 +3722,59 @@
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E60" s="3">
         <v>9400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>7300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>12500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>6200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>4900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>4500</v>
       </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3647,56 +3787,59 @@
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>100</v>
+      </c>
+      <c r="E61" s="3">
         <v>72900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>72600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>65000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>63500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>42400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>41000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>37700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>33100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>31600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3709,8 +3852,11 @@
       <c r="V61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3718,19 +3864,19 @@
         <v>900</v>
       </c>
       <c r="E62" s="3">
+        <v>900</v>
+      </c>
+      <c r="F62" s="3">
         <v>3600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>800</v>
       </c>
       <c r="H62" s="3">
         <v>800</v>
       </c>
       <c r="I62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="J62" s="3">
         <v>700</v>
@@ -3739,26 +3885,26 @@
         <v>700</v>
       </c>
       <c r="L62" s="3">
+        <v>700</v>
+      </c>
+      <c r="M62" s="3">
         <v>800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>600</v>
       </c>
       <c r="P62" s="3">
         <v>600</v>
       </c>
       <c r="Q62" s="3">
+        <v>600</v>
+      </c>
+      <c r="R62" s="3">
         <v>500</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3771,8 +3917,11 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3833,8 +3982,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3895,8 +4047,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3957,56 +4112,59 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7100</v>
+      </c>
+      <c r="E66" s="3">
         <v>83200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>83700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>78800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>52100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>51000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>47300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>48500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>46300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>52800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>8200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5100</v>
       </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4019,8 +4177,11 @@
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4043,8 +4204,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4105,8 +4267,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4167,8 +4332,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4229,8 +4397,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4291,56 +4462,59 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-221800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-227100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-212900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-200000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-183900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-158000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-147400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-138000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-127700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-117600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-102800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-107400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-94100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-61200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-50100</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4353,8 +4527,11 @@
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4415,8 +4592,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4477,8 +4657,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4539,56 +4722,59 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E76" s="3">
         <v>-8400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>25500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>35000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>53600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>63200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>71300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>62700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>67900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>75900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>55700</v>
       </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4601,8 +4787,11 @@
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4663,137 +4852,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-14300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-12900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-25900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-10600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-9400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-10300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-13200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-33000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-9500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-5600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-3800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-5900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4816,8 +5014,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4840,23 +5039,23 @@
         <v>100</v>
       </c>
       <c r="J83" s="3">
+        <v>100</v>
+      </c>
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
       <c r="L83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M83" s="3">
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
         <v>0</v>
       </c>
@@ -4872,14 +5071,17 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
+      <c r="U83" s="3">
+        <v>0</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4940,8 +5142,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5002,8 +5207,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5064,8 +5272,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5126,8 +5337,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5188,70 +5402,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-7200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-7900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-5200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-10600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-4800</v>
       </c>
       <c r="R89" s="3">
         <v>-4800</v>
       </c>
       <c r="S89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="T89" s="3">
         <v>-1500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-2300</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5274,70 +5494,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-1300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-10000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>100</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
         <v>0</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
+      <c r="U91" s="3">
+        <v>0</v>
       </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5398,8 +5622,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5460,70 +5687,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="E94" s="3">
         <v>-400</v>
       </c>
       <c r="F94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G94" s="3">
         <v>-1300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-3000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5546,8 +5779,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5575,8 +5809,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -5608,8 +5842,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5670,8 +5907,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5732,8 +5972,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5794,26 +6037,29 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E100" s="3">
         <v>-300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>8700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>5500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>13200</v>
       </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
       <c r="I100" s="3">
         <v>0</v>
       </c>
@@ -5821,43 +6067,46 @@
         <v>0</v>
       </c>
       <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
         <v>1300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>56100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>2100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>27300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2800</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5879,105 +6128,111 @@
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>100</v>
       </c>
-      <c r="U101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-6000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-9800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-8500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-20600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-17500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-4300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4600</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -3536,7 +3536,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6100</v>
+        <v>1100</v>
       </c>
       <c r="E57" s="3">
         <v>1500</v>
@@ -3665,8 +3665,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>3200</v>
       </c>
       <c r="E59" s="3">
         <v>3400</v>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,113 +656,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44196</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44104</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -799,8 +802,8 @@
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O8" s="3">
-        <v>0</v>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P8" s="3">
         <v>0</v>
@@ -832,47 +835,50 @@
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E9" s="3">
         <v>2000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
@@ -903,47 +909,50 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-1500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-2800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-3100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-1200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
@@ -974,8 +983,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1001,8 +1013,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1021,59 +1034,62 @@
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L12" s="3">
         <v>0</v>
       </c>
       <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="N12" s="3">
-        <v>0</v>
-      </c>
       <c r="O12" s="3">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3">
         <v>3400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3200</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1900</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>800</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>2500</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>400</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>300</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1143,47 +1159,50 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>-17300</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>21000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>900</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1199,8 +1218,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1214,16 +1233,19 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E15" s="3">
         <v>5300</v>
-      </c>
-      <c r="E15" s="3">
-        <v>5000</v>
       </c>
       <c r="F15" s="3">
         <v>5000</v>
@@ -1238,7 +1260,7 @@
         <v>5000</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="K15" s="3">
         <v>100</v>
@@ -1253,7 +1275,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1279,14 +1301,17 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>3</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1309,150 +1334,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E17" s="3">
         <v>10700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>10200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>15100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>8900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>8600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>13400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>33000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>6100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5000</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-9600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-10200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-11000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-12900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-15100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-4200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-8900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-7700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-8700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-7400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-11200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-8600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-13400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-33000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-10800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-6100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-2700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-5000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1478,8 +1510,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1493,17 +1526,17 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
@@ -1517,111 +1550,117 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-1700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>14000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-4600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-5200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-5800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-9300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-8800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-8600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-7300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-32900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-11000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-9400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-3800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-5900</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1632,43 +1671,43 @@
         <v>0</v>
       </c>
       <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
         <v>1900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1700</v>
-      </c>
-      <c r="L22" s="3">
-        <v>1800</v>
       </c>
       <c r="M22" s="3">
         <v>1800</v>
       </c>
       <c r="N22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O22" s="3">
         <v>2200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1685,97 +1724,103 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
+      <c r="X22" s="3">
+        <v>0</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-9500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-14300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-16100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-25900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-10600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-9400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-14900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>4600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-13200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-33000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-11000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-5600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-5900</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E24" s="3">
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1800,8 +1845,8 @@
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P24" s="3">
         <v>0</v>
@@ -1833,8 +1878,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1904,150 +1952,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-14300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-12900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-16100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-25900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-9400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-10300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-13200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-33000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-9500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-5900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-14300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-12900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-16100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-25900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-9400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-10300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>4600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-13200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-33000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-11000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-9500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-5600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-5900</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2117,8 +2174,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2188,8 +2248,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2259,8 +2322,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2330,8 +2396,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2345,17 +2414,17 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
+        <v>0</v>
+      </c>
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
@@ -2369,111 +2438,117 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>1700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-14000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-14300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-12900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-16100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-25900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-9400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-10300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>4600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-13200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-33000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-11000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-9500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-5600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-3800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-5900</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2543,155 +2618,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-14300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-12900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-16100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-25900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-9400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-10300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>4600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-13200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-33000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-11000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-9500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-5600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-3800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-5900</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44196</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44104</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2717,8 +2801,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2744,65 +2829,66 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>600</v>
+      </c>
+      <c r="E41" s="3">
         <v>5500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>20300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>56800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>31100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>41100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>53700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>34700</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2815,8 +2901,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2886,8 +2975,11 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2924,8 +3016,8 @@
       <c r="N43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P43" s="3">
         <v>0</v>
@@ -2957,8 +3049,11 @@
       <c r="Y43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2995,8 +3090,8 @@
       <c r="N44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -3028,13 +3123,16 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>300</v>
       </c>
       <c r="E45" s="3" t="s">
         <v>3</v>
@@ -3066,27 +3164,27 @@
       <c r="N45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>1000</v>
-      </c>
-      <c r="P45" s="3">
-        <v>1500</v>
       </c>
       <c r="Q45" s="3">
         <v>1500</v>
       </c>
       <c r="R45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="S45" s="3">
         <v>3200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3099,65 +3197,68 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E46" s="3">
         <v>5900</v>
-      </c>
-      <c r="E46" s="3">
-        <v>4600</v>
       </c>
       <c r="F46" s="3">
         <v>4600</v>
       </c>
       <c r="G46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="H46" s="3">
         <v>1500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>22100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>38100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>57800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>75700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>32600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>44300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>54200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>34900</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3170,8 +3271,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3208,8 +3312,8 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3241,65 +3345,68 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E48" s="3">
         <v>61200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>64600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>68500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>73100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>77300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>82400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>86700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>83300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>82400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>78500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>72500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>58700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>44800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>37200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>29500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>26400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>24800</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3312,8 +3419,11 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3383,8 +3493,11 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3454,8 +3567,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3525,8 +3641,11 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3534,10 +3653,10 @@
         <v>1600</v>
       </c>
       <c r="E52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="3">
         <v>1500</v>
-      </c>
-      <c r="F52" s="3">
-        <v>300</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
@@ -3561,7 +3680,7 @@
         <v>300</v>
       </c>
       <c r="N52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="O52" s="3">
         <v>1100</v>
@@ -3581,8 +3700,8 @@
       <c r="T52" s="3">
         <v>1100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
+      <c r="U52" s="3">
+        <v>1100</v>
       </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
@@ -3596,8 +3715,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3667,65 +3789,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E54" s="3">
         <v>68700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>70700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>73400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>74800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>85800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>89500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>87100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>95700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>100900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>111600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>117600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>121700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>70900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>74900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>81700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>60700</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3738,8 +3863,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3765,8 +3893,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3792,64 +3921,65 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>2600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1100</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1500</v>
       </c>
       <c r="H57" s="3">
         <v>1500</v>
       </c>
       <c r="I57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J57" s="3">
         <v>900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>4700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>6100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>4300</v>
       </c>
       <c r="T57" s="3">
         <v>4300</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>4300</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3863,8 +3993,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3881,7 +4014,7 @@
         <v>100</v>
       </c>
       <c r="H58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I58" s="3">
         <v>200</v>
@@ -3890,10 +4023,10 @@
         <v>200</v>
       </c>
       <c r="K58" s="3">
+        <v>200</v>
+      </c>
+      <c r="L58" s="3">
         <v>100</v>
-      </c>
-      <c r="L58" s="3">
-        <v>200</v>
       </c>
       <c r="M58" s="3">
         <v>200</v>
@@ -3902,13 +4035,13 @@
         <v>200</v>
       </c>
       <c r="O58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>0</v>
       </c>
       <c r="R58" s="3" t="s">
         <v>3</v>
@@ -3922,8 +4055,8 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
+      <c r="V58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W58" s="3">
         <v>0</v>
@@ -3934,8 +4067,11 @@
       <c r="Y58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -3943,56 +4079,56 @@
         <v>2800</v>
       </c>
       <c r="E59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F59" s="3">
+        <v>3700</v>
+      </c>
+      <c r="G59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>2900</v>
+      </c>
+      <c r="J59" s="3">
+        <v>3300</v>
+      </c>
+      <c r="K59" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="M59" s="3">
+        <v>4500</v>
+      </c>
+      <c r="N59" s="3">
+        <v>3400</v>
+      </c>
+      <c r="O59" s="3">
+        <v>8700</v>
+      </c>
+      <c r="P59" s="3">
+        <v>9600</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>4800</v>
+      </c>
+      <c r="R59" s="3">
         <v>200</v>
       </c>
-      <c r="F59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="H59" s="3">
-        <v>2900</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3100</v>
-      </c>
-      <c r="K59" s="3">
-        <v>2800</v>
-      </c>
-      <c r="L59" s="3">
-        <v>4500</v>
-      </c>
-      <c r="M59" s="3">
-        <v>3400</v>
-      </c>
-      <c r="N59" s="3">
-        <v>8700</v>
-      </c>
-      <c r="O59" s="3">
-        <v>9600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>4800</v>
-      </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
+        <v>100</v>
+      </c>
+      <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
         <v>200</v>
       </c>
-      <c r="R59" s="3">
-        <v>100</v>
-      </c>
-      <c r="S59" s="3">
-        <v>600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>200</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4005,65 +4141,68 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E60" s="3">
         <v>7400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>7300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>12500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>9600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>6200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>4900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4500</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4076,13 +4215,16 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
         <v>100</v>
@@ -4091,50 +4233,50 @@
         <v>100</v>
       </c>
       <c r="G61" s="3">
+        <v>100</v>
+      </c>
+      <c r="H61" s="3">
         <v>72900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>72600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>65000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>63500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>42400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>41000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>33100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>31600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4147,37 +4289,40 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="E62" s="3">
         <v>1000</v>
       </c>
       <c r="F62" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
         <v>900</v>
       </c>
       <c r="H62" s="3">
+        <v>900</v>
+      </c>
+      <c r="I62" s="3">
         <v>3600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>4100</v>
-      </c>
-      <c r="J62" s="3">
-        <v>800</v>
       </c>
       <c r="K62" s="3">
         <v>800</v>
       </c>
       <c r="L62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M62" s="3">
         <v>700</v>
@@ -4186,26 +4331,26 @@
         <v>700</v>
       </c>
       <c r="O62" s="3">
+        <v>700</v>
+      </c>
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>700</v>
-      </c>
-      <c r="R62" s="3">
-        <v>600</v>
       </c>
       <c r="S62" s="3">
         <v>600</v>
       </c>
       <c r="T62" s="3">
+        <v>600</v>
+      </c>
+      <c r="U62" s="3">
         <v>500</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4363,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4289,8 +4437,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4360,8 +4511,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4431,65 +4585,68 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E66" s="3">
         <v>8500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>83200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>78800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>71500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>52100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>51000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>47300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>48500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>46300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>52800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>8200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4502,8 +4659,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4529,8 +4689,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4600,8 +4761,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4671,8 +4835,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4742,8 +4909,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4813,65 +4983,68 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-253100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-242200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-231600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-221800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-227100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-212900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-200000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-183900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-158000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-147400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-138000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-127700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-117600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-102800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-107400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-94100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-61200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-50100</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4884,8 +5057,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4955,8 +5131,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5026,8 +5205,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5097,65 +5279,68 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>51600</v>
+      </c>
+      <c r="E76" s="3">
         <v>60200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>63200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>66300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-8400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>35000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>44800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>53600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>63200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>71300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>68800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>62700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>67900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>75900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>55700</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5168,8 +5353,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5239,155 +5427,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44196</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44104</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-14300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-12900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-16100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-25900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-9400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-10300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>4600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-13200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-33000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-11000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-9500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-5600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-3800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-5900</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5413,8 +5610,9 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5422,10 +5620,10 @@
         <v>5000</v>
       </c>
       <c r="E83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F83" s="3">
         <v>5100</v>
-      </c>
-      <c r="F83" s="3">
-        <v>100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -5446,23 +5644,23 @@
         <v>100</v>
       </c>
       <c r="M83" s="3">
+        <v>100</v>
+      </c>
+      <c r="N83" s="3">
         <v>200</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
       <c r="O83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P83" s="3">
         <v>100</v>
       </c>
       <c r="Q83" s="3">
+        <v>100</v>
+      </c>
+      <c r="R83" s="3">
         <v>200</v>
       </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
@@ -5478,14 +5676,17 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
+      <c r="X83" s="3">
+        <v>0</v>
       </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5555,8 +5756,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5626,8 +5830,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5697,8 +5904,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5768,8 +5978,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5839,79 +6052,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-4300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-6200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-5700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-6400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-7200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-4900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-7900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-8400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-5200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-10600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-4800</v>
       </c>
       <c r="U89" s="3">
         <v>-4800</v>
       </c>
       <c r="V89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="W89" s="3">
         <v>-1500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-2300</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5937,79 +6156,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1400</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-600</v>
       </c>
       <c r="F91" s="3">
         <v>-600</v>
       </c>
       <c r="G91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-10000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-13900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>100</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
+      <c r="X91" s="3">
+        <v>0</v>
       </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6079,8 +6302,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6150,8 +6376,11 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -6159,70 +6388,73 @@
         <v>-1400</v>
       </c>
       <c r="E94" s="3">
-        <v>-600</v>
+        <v>-1400</v>
       </c>
       <c r="F94" s="3">
         <v>-600</v>
       </c>
       <c r="G94" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="H94" s="3">
         <v>-400</v>
       </c>
       <c r="I94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6248,8 +6480,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6286,8 +6519,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -6319,8 +6552,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6390,8 +6626,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6461,8 +6700,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6532,35 +6774,38 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E100" s="3">
         <v>7400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>13200</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
       <c r="L100" s="3">
         <v>0</v>
       </c>
@@ -6568,43 +6813,46 @@
         <v>0</v>
       </c>
       <c r="N100" s="3">
+        <v>0</v>
+      </c>
+      <c r="O100" s="3">
         <v>1300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>56100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>2100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>27300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2800</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6635,114 +6883,120 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-300</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>-200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>100</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E102" s="3">
         <v>1600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-3100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-9800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-20600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-17500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-6100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4600</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FEAM_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="92">
   <si>
     <t>FEAM</t>
   </si>
@@ -656,116 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -805,8 +809,8 @@
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -838,50 +842,53 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E9" s="3">
         <v>2600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -912,50 +919,53 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-2600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-2000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-1500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-1900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-2800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-3600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-1200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-1400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-1600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-1700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-1300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -986,8 +996,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1014,8 +1027,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1037,59 +1051,62 @@
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3">
-        <v>0</v>
+      <c r="J12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M12" s="3">
         <v>0</v>
       </c>
       <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="O12" s="3">
-        <v>0</v>
-      </c>
       <c r="P12" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3">
         <v>3400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3200</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1900</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>2500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>400</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>300</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1162,50 +1179,53 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>1600</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>-17300</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>21000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>900</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1221,8 +1241,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1236,19 +1256,22 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E15" s="3">
         <v>5400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>5000</v>
       </c>
       <c r="G15" s="3">
         <v>5000</v>
@@ -1263,7 +1286,7 @@
         <v>5000</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
@@ -1278,7 +1301,7 @@
         <v>100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1304,14 +1327,17 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>3</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1335,156 +1361,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E17" s="3">
         <v>10900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>15100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>7700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>8600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>33000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>10600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5000</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-10900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-10700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-9600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-10200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-11000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-12900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-15100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-8900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-7700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-8700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-7400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-8600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-13400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-33000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-10800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-10600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-6100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-2700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-5000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1511,13 +1544,14 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1529,17 +1563,17 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1553,114 +1587,120 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>14000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-5500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-5400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-4600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-5200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-6900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-5800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-9300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-8800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-8600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-7300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-13100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-32900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-11000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-9400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-3800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1674,43 +1714,43 @@
         <v>0</v>
       </c>
       <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
         <v>1900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1700</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1800</v>
       </c>
       <c r="N22" s="3">
         <v>1800</v>
       </c>
       <c r="O22" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P22" s="3">
         <v>2200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>800</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S22" s="3">
-        <v>0</v>
+      <c r="S22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T22" s="3">
         <v>0</v>
@@ -1727,88 +1767,94 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
+      <c r="Y22" s="3">
+        <v>0</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-10900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-10700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-9500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-14300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-16100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-25900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-9400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>4600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-13200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-33000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-11000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-9500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-5600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1818,12 +1864,12 @@
       <c r="E24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F24" s="3">
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1848,8 +1894,8 @@
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1881,8 +1927,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1955,156 +2004,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-10900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-10700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-14300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-12900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-16100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-25900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-9400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-10300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-10100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>4600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-13200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-33000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-9500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-10900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-10700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-14300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-12900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-16100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-25900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-9400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-10300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-10100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>4600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-13200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-33000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-11000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-9500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-5600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2177,8 +2235,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2251,8 +2312,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2325,8 +2389,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2399,13 +2466,16 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2417,17 +2487,17 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -2441,114 +2511,120 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-14000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-10900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-10700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-14300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-12900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-16100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-25900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-9400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-10300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-10100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>4600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-13200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-33000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-11000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-9500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-5600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2621,161 +2697,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-10900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-10700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-14300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-12900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-16100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-25900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-9400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-10300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-10100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>4600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-13200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-33000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-11000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-9500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-5600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2802,8 +2887,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2830,68 +2916,69 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E41" s="3">
         <v>600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>4000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>20300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>56800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>74200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>31100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>41100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>53700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>34700</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2904,8 +2991,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2978,8 +3068,11 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3019,8 +3112,8 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -3052,8 +3145,11 @@
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3093,8 +3189,8 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3126,17 +3222,20 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>300</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3167,27 +3266,27 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3">
         <v>1000</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>1500</v>
       </c>
       <c r="R45" s="3">
         <v>1500</v>
       </c>
       <c r="S45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="T45" s="3">
         <v>3200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3200,68 +3299,71 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E46" s="3">
         <v>1100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5900</v>
-      </c>
-      <c r="F46" s="3">
-        <v>4600</v>
       </c>
       <c r="G46" s="3">
         <v>4600</v>
       </c>
       <c r="H46" s="3">
+        <v>4600</v>
+      </c>
+      <c r="I46" s="3">
         <v>1500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>22100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>38100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>57800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>75700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>32600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>44300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>54200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>34900</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,8 +3376,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3315,8 +3420,8 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -3348,68 +3453,71 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>50700</v>
+      </c>
+      <c r="E48" s="3">
         <v>55900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>61200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>64600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>68500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>73100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>77300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>82400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>86700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>83300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>82400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>78500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>72500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>58700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>44800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>37200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>26400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>24800</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3422,8 +3530,11 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3496,8 +3607,11 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3570,8 +3684,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3644,8 +3761,11 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3656,10 +3776,10 @@
         <v>1600</v>
       </c>
       <c r="F52" s="3">
+        <v>1600</v>
+      </c>
+      <c r="G52" s="3">
         <v>1500</v>
-      </c>
-      <c r="G52" s="3">
-        <v>300</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
@@ -3683,7 +3803,7 @@
         <v>300</v>
       </c>
       <c r="O52" s="3">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="P52" s="3">
         <v>1100</v>
@@ -3703,8 +3823,8 @@
       <c r="U52" s="3">
         <v>1100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
+      <c r="V52" s="3">
+        <v>1100</v>
       </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
@@ -3718,8 +3838,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3792,68 +3915,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>78100</v>
+      </c>
+      <c r="E54" s="3">
         <v>58600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>70700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>73400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>74800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>85800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>89500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>87100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>95700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>100900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>111600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>117600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>121700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>70900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>74900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>81700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60700</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3866,8 +3992,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3894,8 +4023,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3922,67 +4052,68 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
-      </c>
-      <c r="H57" s="3">
-        <v>1500</v>
       </c>
       <c r="I57" s="3">
         <v>1500</v>
       </c>
       <c r="J57" s="3">
+        <v>1500</v>
+      </c>
+      <c r="K57" s="3">
         <v>900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>4700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6100</v>
-      </c>
-      <c r="T57" s="3">
-        <v>4300</v>
       </c>
       <c r="U57" s="3">
         <v>4300</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>4300</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3996,8 +4127,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4017,7 +4151,7 @@
         <v>100</v>
       </c>
       <c r="I58" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="J58" s="3">
         <v>200</v>
@@ -4026,10 +4160,10 @@
         <v>200</v>
       </c>
       <c r="L58" s="3">
+        <v>200</v>
+      </c>
+      <c r="M58" s="3">
         <v>100</v>
-      </c>
-      <c r="M58" s="3">
-        <v>200</v>
       </c>
       <c r="N58" s="3">
         <v>200</v>
@@ -4038,13 +4172,13 @@
         <v>200</v>
       </c>
       <c r="P58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="R58" s="3">
+        <v>0</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -4058,8 +4192,8 @@
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W58" s="3">
-        <v>0</v>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X58" s="3">
         <v>0</v>
@@ -4070,68 +4204,71 @@
       <c r="Z58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>2800</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E59" s="3">
         <v>2800</v>
       </c>
       <c r="F59" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G59" s="3">
         <v>3700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>4500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>8700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>200</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4144,68 +4281,71 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>4000</v>
+      </c>
+      <c r="E60" s="3">
         <v>5900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>6400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>7500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>7300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>9000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>11500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>12500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>6200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>4900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4500</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4218,8 +4358,11 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -4227,7 +4370,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>100</v>
@@ -4236,50 +4379,50 @@
         <v>100</v>
       </c>
       <c r="H61" s="3">
+        <v>100</v>
+      </c>
+      <c r="I61" s="3">
         <v>72900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>72600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>65000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>63500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>42400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>41000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>36300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>33100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>31600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>100</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4292,8 +4435,11 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4301,31 +4447,31 @@
         <v>1100</v>
       </c>
       <c r="E62" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="F62" s="3">
         <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="H62" s="3">
         <v>900</v>
       </c>
       <c r="I62" s="3">
+        <v>900</v>
+      </c>
+      <c r="J62" s="3">
         <v>3600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>4100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>800</v>
       </c>
       <c r="L62" s="3">
         <v>800</v>
       </c>
       <c r="M62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="N62" s="3">
         <v>700</v>
@@ -4334,26 +4480,26 @@
         <v>700</v>
       </c>
       <c r="P62" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>700</v>
-      </c>
-      <c r="S62" s="3">
-        <v>600</v>
       </c>
       <c r="T62" s="3">
         <v>600</v>
       </c>
       <c r="U62" s="3">
+        <v>600</v>
+      </c>
+      <c r="V62" s="3">
         <v>500</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4366,8 +4512,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4440,8 +4589,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4514,8 +4666,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4588,68 +4743,71 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E66" s="3">
         <v>7000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>8500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>83200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>83700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>78800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>71500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>51000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>47300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>48500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>46300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>52800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>8200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4662,8 +4820,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4690,8 +4851,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4764,8 +4926,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4838,8 +5003,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4912,8 +5080,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4986,68 +5157,71 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-265300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-253100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-242200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-231600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-221800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-227100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-212900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-200000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-183900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-158000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-147400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-138000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-127700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-117600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-102800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-107400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-94100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-61200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-50100</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5060,8 +5234,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5134,8 +5311,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5208,8 +5388,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5282,68 +5465,71 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>73000</v>
+      </c>
+      <c r="E76" s="3">
         <v>51600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>60200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>63200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>66300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-8400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>25500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>35000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>44800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>53600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>63200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>71300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>68800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>62700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>67900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>75900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>55700</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5356,8 +5542,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5430,161 +5619,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-10900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-10700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-14300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-12900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-16100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-25900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-9400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-10300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-10100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>4600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-13200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-33000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-11000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-9500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-5600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5611,8 +5809,9 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5623,10 +5822,10 @@
         <v>5000</v>
       </c>
       <c r="F83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G83" s="3">
         <v>5100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -5647,23 +5846,23 @@
         <v>100</v>
       </c>
       <c r="N83" s="3">
+        <v>100</v>
+      </c>
+      <c r="O83" s="3">
         <v>200</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
       <c r="P83" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q83" s="3">
         <v>100</v>
       </c>
       <c r="R83" s="3">
+        <v>100</v>
+      </c>
+      <c r="S83" s="3">
         <v>200</v>
       </c>
-      <c r="S83" s="3">
-        <v>0</v>
-      </c>
       <c r="T83" s="3">
         <v>0</v>
       </c>
@@ -5679,14 +5878,17 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
+      <c r="Y83" s="3">
+        <v>0</v>
       </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5759,8 +5961,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5833,8 +6038,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5907,8 +6115,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5981,8 +6192,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6055,82 +6269,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-4300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-6200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-5700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-7200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-4900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-7900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-5200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-10600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-8000</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-4800</v>
       </c>
       <c r="V89" s="3">
         <v>-4800</v>
       </c>
       <c r="W89" s="3">
+        <v>-4800</v>
+      </c>
+      <c r="X89" s="3">
         <v>-1500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6157,82 +6377,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1400</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-600</v>
       </c>
       <c r="G91" s="3">
         <v>-600</v>
       </c>
       <c r="H91" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-13900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>100</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
       <c r="X91" s="3">
         <v>0</v>
       </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
+      <c r="Y91" s="3">
+        <v>0</v>
       </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6305,8 +6529,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6379,82 +6606,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1400</v>
+        <v>-4500</v>
       </c>
       <c r="E94" s="3">
         <v>-1400</v>
       </c>
       <c r="F94" s="3">
-        <v>-600</v>
+        <v>-1400</v>
       </c>
       <c r="G94" s="3">
         <v>-600</v>
       </c>
       <c r="H94" s="3">
-        <v>-400</v>
+        <v>-600</v>
       </c>
       <c r="I94" s="3">
         <v>-400</v>
       </c>
       <c r="J94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-1300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6481,8 +6714,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6522,8 +6756,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -6555,8 +6789,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6629,8 +6866,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6703,8 +6943,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6777,38 +7020,41 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>33600</v>
+      </c>
+      <c r="E100" s="3">
         <v>1700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>7400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>9600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>13200</v>
       </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
       <c r="M100" s="3">
         <v>0</v>
       </c>
@@ -6816,43 +7062,46 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
+        <v>0</v>
+      </c>
+      <c r="P100" s="3">
         <v>1300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>56100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>2100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>27300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>1100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2800</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6886,117 +7135,123 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3">
         <v>-200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-300</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
       <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
         <v>-200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>100</v>
       </c>
-      <c r="Y101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-3100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>5900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-9800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-15800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-20600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>43100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-6100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
